--- a/examples/example-workbook.xlsx
+++ b/examples/example-workbook.xlsx
@@ -446,12 +446,15 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
       <c r="E3">
         <f>D3*1.2</f>
+        <v>0</v>
       </c>
       <c r="F3">
         <f>(D3-B3)/D3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -466,12 +469,15 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>D4*1.2</f>
+        <v>0</v>
       </c>
       <c r="F4">
         <f>(D4-B4)/D4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -486,12 +492,15 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
       <c r="E5">
         <f>D5*1.2</f>
+        <v>0</v>
       </c>
       <c r="F5">
         <f>(D5-B5)/D5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -506,12 +515,15 @@
       </c>
       <c r="D6">
         <f>B6*C6</f>
+        <v>0</v>
       </c>
       <c r="E6">
         <f>D6*1.2</f>
+        <v>0</v>
       </c>
       <c r="F6">
         <f>(D6-B6)/D6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -526,12 +538,15 @@
       </c>
       <c r="D7">
         <f>B7*C7</f>
+        <v>0</v>
       </c>
       <c r="E7">
         <f>D7*1.2</f>
+        <v>0</v>
       </c>
       <c r="F7">
         <f>(D7-B7)/D7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -546,12 +561,15 @@
       </c>
       <c r="D8">
         <f>B8*C8</f>
+        <v>0</v>
       </c>
       <c r="E8">
         <f>D8*1.2</f>
+        <v>0</v>
       </c>
       <c r="F8">
         <f>(D8-B8)/D8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -566,12 +584,15 @@
       </c>
       <c r="D9">
         <f>B9*C9</f>
+        <v>0</v>
       </c>
       <c r="E9">
         <f>D9*1.2</f>
+        <v>0</v>
       </c>
       <c r="F9">
         <f>(D9-B9)/D9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -586,12 +607,15 @@
       </c>
       <c r="D10">
         <f>B10*C10</f>
+        <v>0</v>
       </c>
       <c r="E10">
         <f>D10*1.2</f>
+        <v>0</v>
       </c>
       <c r="F10">
         <f>(D10-B10)/D10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -606,12 +630,15 @@
       </c>
       <c r="D11">
         <f>B11*C11</f>
+        <v>0</v>
       </c>
       <c r="E11">
         <f>D11*1.2</f>
+        <v>0</v>
       </c>
       <c r="F11">
         <f>(D11-B11)/D11</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -626,12 +653,15 @@
       </c>
       <c r="D12">
         <f>B12*C12</f>
+        <v>0</v>
       </c>
       <c r="E12">
         <f>D12*1.2</f>
+        <v>0</v>
       </c>
       <c r="F12">
         <f>(D12-B12)/D12</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -646,12 +676,15 @@
       </c>
       <c r="D13">
         <f>B13*C13</f>
+        <v>0</v>
       </c>
       <c r="E13">
         <f>D13*1.2</f>
+        <v>0</v>
       </c>
       <c r="F13">
         <f>(D13-B13)/D13</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -666,12 +699,15 @@
       </c>
       <c r="D14">
         <f>B14*C14</f>
+        <v>0</v>
       </c>
       <c r="E14">
         <f>D14*1.2</f>
+        <v>0</v>
       </c>
       <c r="F14">
         <f>(D14-B14)/B14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -686,12 +722,15 @@
       </c>
       <c r="D15">
         <f>B15*C15</f>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>D15*1.2</f>
+        <v>0</v>
       </c>
       <c r="F15">
         <f>(D15-B15)/D15</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -706,12 +745,15 @@
       </c>
       <c r="D16">
         <f>B16*C16</f>
+        <v>0</v>
       </c>
       <c r="E16">
         <f>D16*1.2</f>
+        <v>0</v>
       </c>
       <c r="F16">
         <f>(D16-B16)/D16</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -726,12 +768,15 @@
       </c>
       <c r="D17">
         <f>B17*C17</f>
+        <v>0</v>
       </c>
       <c r="E17">
         <f>D17*1.2</f>
+        <v>0</v>
       </c>
       <c r="F17">
         <f>(D17-B17)/D17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -746,12 +791,15 @@
       </c>
       <c r="D18">
         <f>B18*C18</f>
+        <v>0</v>
       </c>
       <c r="E18">
         <f>D18*1.2</f>
+        <v>0</v>
       </c>
       <c r="F18">
         <f>(D18-B18)/D18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -766,12 +814,15 @@
       </c>
       <c r="D19">
         <f>B19*C19</f>
+        <v>0</v>
       </c>
       <c r="E19">
         <f>D19*1.2</f>
+        <v>0</v>
       </c>
       <c r="F19">
         <f>(D19-B19)/D19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -786,12 +837,15 @@
       </c>
       <c r="D20">
         <f>B20*C20</f>
+        <v>0</v>
       </c>
       <c r="E20">
         <f>D20*1.2</f>
+        <v>0</v>
       </c>
       <c r="F20">
         <f>(D20-B20)/D20</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -806,12 +860,15 @@
       </c>
       <c r="D21">
         <f>B21*C21</f>
+        <v>0</v>
       </c>
       <c r="E21">
         <f>D21*1.2</f>
+        <v>0</v>
       </c>
       <c r="F21">
         <f>(D21-B21)/D21</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -826,12 +883,15 @@
       </c>
       <c r="D22">
         <f>B22*C22</f>
+        <v>0</v>
       </c>
       <c r="E22">
         <f>D22*1.2</f>
+        <v>0</v>
       </c>
       <c r="F22">
         <f>(D22-B22)/D22</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -846,12 +906,15 @@
       </c>
       <c r="D23">
         <f>B23*C23</f>
+        <v>0</v>
       </c>
       <c r="E23">
         <f>D23*1.2</f>
+        <v>0</v>
       </c>
       <c r="F23">
         <f>(D23-B23)/D23</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -866,12 +929,15 @@
       </c>
       <c r="D24">
         <f>B24*C24</f>
+        <v>0</v>
       </c>
       <c r="E24">
         <f>D24*1.2</f>
+        <v>0</v>
       </c>
       <c r="F24">
         <f>(D24-B24)/D24</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -886,12 +952,15 @@
       </c>
       <c r="D25">
         <f>B25*C25</f>
+        <v>0</v>
       </c>
       <c r="E25">
         <f>D25*1.2</f>
+        <v>0</v>
       </c>
       <c r="F25">
         <f>(D25-B25)/D25</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -906,12 +975,15 @@
       </c>
       <c r="D26">
         <f>B26*C26</f>
+        <v>0</v>
       </c>
       <c r="E26">
         <f>D26*1.2</f>
+        <v>0</v>
       </c>
       <c r="F26">
         <f>(D26-B26)/D26</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -926,9 +998,11 @@
       </c>
       <c r="D27">
         <f>B27*C27</f>
+        <v>0</v>
       </c>
       <c r="E27">
         <f>D27*1.2</f>
+        <v>0</v>
       </c>
       <c r="F27" t="e">
         <v>#DIV/0!</v>
@@ -1022,6 +1096,7 @@
       </c>
       <c r="B3">
         <f>SUM(Pricing!D3:D26)</f>
+        <v>0</v>
       </c>
       <c r="C3" t="str">
         <v>Pricing</v>
@@ -1033,6 +1108,7 @@
       </c>
       <c r="B4">
         <f>SUM(Pricing!E3:E26)</f>
+        <v>0</v>
       </c>
       <c r="C4" t="str">
         <v>Pricing</v>
@@ -1044,6 +1120,7 @@
       </c>
       <c r="B5">
         <f>SUM(INDIRECT("'"&amp;B7&amp;"'!D2:D5"))</f>
+        <v>0</v>
       </c>
       <c r="C5" t="str">
         <v>Whichever sheet B7 names</v>
@@ -1055,6 +1132,7 @@
       </c>
       <c r="B6">
         <f>SUM(OFFSET(Jan!D2,0,0,3,1))</f>
+        <v>0</v>
       </c>
       <c r="C6" t="str">
         <v>Offset from Jan</v>
@@ -1077,6 +1155,7 @@
       </c>
       <c r="B8">
         <f>IF(B3&gt;0,IF(B4&gt;0,IF(B5&gt;0,IF(B6&gt;0,INDEX(Pricing!F3:F26,MATCH(MAX(Pricing!F3:F26),Pricing!F3:F26,0))*0.4+INDEX(Pricing!F3:F26,MATCH(MIN(Pricing!F3:F26),Pricing!F3:F26,0))*0.6,0),0),0),0)</f>
+        <v>0</v>
       </c>
       <c r="C8" t="str">
         <v>Do not touch</v>
@@ -1119,6 +1198,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1133,6 +1213,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1147,6 +1228,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1161,6 +1243,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1200,6 +1283,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1214,6 +1298,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1228,6 +1313,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1242,6 +1328,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1281,6 +1368,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1295,6 +1383,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1309,6 +1398,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1323,6 +1413,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1362,6 +1453,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1376,6 +1468,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1390,6 +1483,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1404,6 +1498,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1443,6 +1538,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1457,6 +1553,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1471,6 +1568,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1485,6 +1583,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1524,6 +1623,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1538,6 +1638,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1552,6 +1653,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1566,6 +1668,7 @@
       </c>
       <c r="D5">
         <f>B5*C5</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
